--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-16T14:25:12+00:00</t>
+    <t>2024-12-17T15:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-17T15:13:00+00:00</t>
+    <t>2024-12-20T15:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
+++ b/r4-ELGA-IV-Diabetes-fokuswoche/StructureDefinition-at-iv-allergyintolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-20T15:32:12+00:00</t>
+    <t>2024-12-20T15:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-iv-diabetes/StructureDefinition/at-ips-allergyintolerance</t>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-ips-allergyintolerance</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -687,7 +687,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-iv-diabetes/StructureDefinition/at-ips-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-ips-patient)
 </t>
   </si>
   <si>
@@ -1353,7 +1353,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="88.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
